--- a/ШКОЛКОВО/Теория/№ 18 Нестандартные задачи/№ 18 Курьер на самокате.xlsx
+++ b/ШКОЛКОВО/Теория/№ 18 Нестандартные задачи/№ 18 Курьер на самокате.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misha\PycharmProjects\ЕГЭ\ШКОЛКОВО\Теория\№ 18 Нестандартные задачи\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E0DC5E6-D28D-4B4C-A6F7-9749ECD6006D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E069E5C6-0C35-461D-A092-DD3649D76FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="19425" windowHeight="13950" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>УСЛОВИЕ:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дан файл, в котором есть два поля – красное и зеленое. Зеленое поле – поле подзарядки, проходя по его клетке самокат Курьера заряжается на то число условных едениц, которое указано в этой клетке. Зарядка начинается в левой верхней клетке и заканчивается в правой нижней клетке зеленого поля. Красное поле – поле доставки, по нему Курьеру необходимо доставить заказ из левой верхней клетки в правую нижнюю. Проходя по клетке красного поля, самокат Курьера разряжается на то число условных едениц, которое указано в этой клетке. Если заряд становится меньше или равен нулю, то курьер не может двигаться дальше.
-За один ход Курьер может переместиться на одну клетку вправо или на одну клетку вниз. Выходить за пределы полей Курьер не может. В начальный момент заряд самоката равен нулю. Определите, сможет ли курьер доставить заказ, если сначала пройдет по зеленому полю, а потом по красному.
-Курьер очень предусмотрительный, поэтому старается зарядить свой самокат как можно больше, а при доставке старается потратить как можно меньше энергии.
-В ответе запишите без пробелов и разделителей ДА и остаток заряда если сможет и НЕТ и количество заряда которое ему не хватило, если заказ не будет доставлен.
-</t>
   </si>
   <si>
     <t>1) Переносим зеленую таблицу вниз, к красной</t>
@@ -93,6 +86,13 @@
       </rPr>
       <t>Переносим красную таблицу вниз</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Дан файл, в котором есть два поля – красное и зеленое. Зеленое поле – поле подзарядки, проходя по его клетке самокат Курьера заряжается на то число условных единиц, которое указано в этой клетке. Зарядка начинается в левой верхней клетке и заканчивается в правой нижней клетке зеленого поля. Красное поле – поле доставки, по нему Курьеру необходимо доставить заказ из левой верхней клетки в правую нижнюю. Проходя по клетке красного поля, самокат Курьера разряжается на то число условных единиц, которое указано в этой клетке. Если заряд становится меньше или равен нулю, то курьер не может двигаться дальше.
+За один ход Курьер может переместиться на одну клетку вправо или на одну клетку вниз. Выходить за пределы полей Курьер не может. В начальный момент заряд самоката равен нулю. Определите, сможет ли курьер доставить заказ, если сначала пройдет по зеленому полю, а потом по красному.
+Курьер очень предусмотрительный, поэтому старается зарядить свой самокат как можно больше, а при доставке старается потратить как можно меньше энергии.
+В ответе запишите без пробелов и разделителей ДА и остаток заряда если сможет и НЕТ и количество заряда которое ему не хватило, если заказ не будет доставлен.
+</t>
   </si>
 </sst>
 </file>
@@ -535,7 +535,7 @@
         <v>33</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -602,7 +602,7 @@
         <v>36</v>
       </c>
       <c r="U4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -637,7 +637,7 @@
         <v>30</v>
       </c>
       <c r="U5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>58</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -707,7 +707,7 @@
         <v>60</v>
       </c>
       <c r="U7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -742,7 +742,7 @@
         <v>18</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -777,7 +777,7 @@
         <v>49</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -959,7 +959,7 @@
         <v>52</v>
       </c>
       <c r="U12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -1034,7 +1034,7 @@
         <v>17</v>
       </c>
       <c r="U13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -1109,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="U14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -1256,7 +1256,7 @@
         <v>20</v>
       </c>
       <c r="U16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -1331,7 +1331,7 @@
         <v>41</v>
       </c>
       <c r="U17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
       <c r="U18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
